--- a/backend/data/financials_by_company/0315.HK.xlsx
+++ b/backend/data/financials_by_company/0315.HK.xlsx
@@ -642,148 +642,148 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-1556268</v>
+        <v>-11822</v>
       </c>
       <c r="C2" t="n">
-        <v>0.291</v>
+        <v>0.257</v>
       </c>
       <c r="D2" t="n">
-        <v>2511557000</v>
+        <v>2493242000</v>
       </c>
       <c r="E2" t="n">
-        <v>-5348000</v>
+        <v>-46000</v>
       </c>
       <c r="F2" t="n">
-        <v>-5348000</v>
+        <v>-46000</v>
       </c>
       <c r="G2" t="n">
-        <v>470126000</v>
+        <v>444621000</v>
       </c>
       <c r="H2" t="n">
-        <v>1643996000</v>
+        <v>1696036000</v>
       </c>
       <c r="I2" t="n">
-        <v>2102263000</v>
+        <v>2687832000</v>
       </c>
       <c r="J2" t="n">
-        <v>2506209000</v>
+        <v>2493196000</v>
       </c>
       <c r="K2" t="n">
-        <v>765224000</v>
+        <v>707820000</v>
       </c>
       <c r="L2" t="n">
-        <v>-34194000</v>
+        <v>-75934000</v>
       </c>
       <c r="M2" t="n">
-        <v>102048000</v>
+        <v>111787000</v>
       </c>
       <c r="N2" t="n">
-        <v>67854000</v>
+        <v>35853000</v>
       </c>
       <c r="O2" t="n">
-        <v>473917732</v>
+        <v>444655178</v>
       </c>
       <c r="P2" t="n">
-        <v>470126000</v>
+        <v>444621000</v>
       </c>
       <c r="Q2" t="n">
-        <v>5519595000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>30979000</v>
-      </c>
+        <v>6046638000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>700602000</v>
+        <v>674215000</v>
       </c>
       <c r="T2" t="n">
-        <v>1103919740</v>
+        <v>1114834038</v>
       </c>
       <c r="U2" t="n">
-        <v>1103917568</v>
+        <v>1114587861</v>
       </c>
       <c r="V2" t="n">
-        <v>0.426</v>
+        <v>0.399</v>
       </c>
       <c r="W2" t="n">
-        <v>0.426</v>
+        <v>0.399</v>
       </c>
       <c r="X2" t="n">
-        <v>470126000</v>
+        <v>444621000</v>
       </c>
       <c r="Y2" t="n">
-        <v>470126000</v>
+        <v>444621000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>470126000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>444621000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1983000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>470126000</v>
+        <v>442638000</v>
       </c>
       <c r="AD2" t="n">
-        <v>470126000</v>
+        <v>442638000</v>
       </c>
       <c r="AE2" t="n">
-        <v>193050000</v>
+        <v>153395000</v>
       </c>
       <c r="AF2" t="n">
-        <v>663176000</v>
+        <v>596033000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-34194000</v>
+        <v>-75934000</v>
       </c>
       <c r="AH2" t="n">
-        <v>102048000</v>
+        <v>111787000</v>
       </c>
       <c r="AI2" t="n">
-        <v>67854000</v>
+        <v>35853000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>701656000</v>
+        <v>673670000</v>
       </c>
       <c r="AK2" t="n">
-        <v>3417332000</v>
+        <v>3358806000</v>
       </c>
       <c r="AL2" t="n">
-        <v>929145000</v>
+        <v>984748000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1740985000</v>
+        <v>1785376000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1740985000</v>
+        <v>1785376000</v>
       </c>
       <c r="AO2" t="n">
-        <v>4118988000</v>
+        <v>4032476000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2102263000</v>
+        <v>2687832000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6221251000</v>
+        <v>6720308000</v>
       </c>
       <c r="AR2" t="n">
-        <v>6221251000</v>
+        <v>6720308000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.282</v>
+        <v>0.295</v>
       </c>
       <c r="D3" t="n">
-        <v>2343407000</v>
+        <v>2565487000</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -792,132 +792,130 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>268846000</v>
+        <v>423170000</v>
       </c>
       <c r="H3" t="n">
-        <v>1666056000</v>
+        <v>1740087000</v>
       </c>
       <c r="I3" t="n">
-        <v>2591654000</v>
+        <v>2772477000</v>
       </c>
       <c r="J3" t="n">
-        <v>2343407000</v>
+        <v>2565487000</v>
       </c>
       <c r="K3" t="n">
-        <v>583725000</v>
+        <v>733780000</v>
       </c>
       <c r="L3" t="n">
-        <v>-45443000</v>
+        <v>-101328000</v>
       </c>
       <c r="M3" t="n">
-        <v>130342000</v>
+        <v>133963000</v>
       </c>
       <c r="N3" t="n">
-        <v>84899000</v>
+        <v>32635000</v>
       </c>
       <c r="O3" t="n">
-        <v>268846000</v>
+        <v>423170000</v>
       </c>
       <c r="P3" t="n">
-        <v>268846000</v>
+        <v>423170000</v>
       </c>
       <c r="Q3" t="n">
-        <v>6262510000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>28748000</v>
-      </c>
+        <v>6245165000</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>702434000</v>
+        <v>743622000</v>
       </c>
       <c r="T3" t="n">
-        <v>1105922541</v>
+        <v>1108937476</v>
       </c>
       <c r="U3" t="n">
-        <v>1105815931</v>
+        <v>1108810921</v>
       </c>
       <c r="V3" t="n">
-        <v>0.243</v>
+        <v>0.382</v>
       </c>
       <c r="W3" t="n">
-        <v>0.243</v>
+        <v>0.382</v>
       </c>
       <c r="X3" t="n">
-        <v>268846000</v>
+        <v>423170000</v>
       </c>
       <c r="Y3" t="n">
-        <v>268846000</v>
+        <v>423170000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>268846000</v>
+        <v>423170000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>244000</v>
       </c>
       <c r="AC3" t="n">
-        <v>268846000</v>
+        <v>422926000</v>
       </c>
       <c r="AD3" t="n">
-        <v>268846000</v>
+        <v>422926000</v>
       </c>
       <c r="AE3" t="n">
-        <v>184537000</v>
+        <v>176891000</v>
       </c>
       <c r="AF3" t="n">
-        <v>453383000</v>
+        <v>599817000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-45443000</v>
+        <v>-101328000</v>
       </c>
       <c r="AH3" t="n">
-        <v>130342000</v>
+        <v>133963000</v>
       </c>
       <c r="AI3" t="n">
-        <v>84899000</v>
+        <v>32635000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500374000</v>
+        <v>712120000</v>
       </c>
       <c r="AK3" t="n">
-        <v>3670856000</v>
+        <v>3472688000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1180289000</v>
+        <v>988964000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1759682000</v>
+        <v>1831707000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1759682000</v>
+        <v>1831707000</v>
       </c>
       <c r="AO3" t="n">
-        <v>4171230000</v>
+        <v>4184808000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2591654000</v>
+        <v>2772477000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6762884000</v>
+        <v>6957285000</v>
       </c>
       <c r="AR3" t="n">
-        <v>6762884000</v>
+        <v>6957285000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.295</v>
+        <v>0.282</v>
       </c>
       <c r="D4" t="n">
-        <v>2565487000</v>
+        <v>2343407000</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -926,248 +924,250 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>423170000</v>
+        <v>268846000</v>
       </c>
       <c r="H4" t="n">
-        <v>1740087000</v>
+        <v>1666056000</v>
       </c>
       <c r="I4" t="n">
-        <v>2772477000</v>
+        <v>2591654000</v>
       </c>
       <c r="J4" t="n">
-        <v>2565487000</v>
+        <v>2343407000</v>
       </c>
       <c r="K4" t="n">
-        <v>733780000</v>
+        <v>583725000</v>
       </c>
       <c r="L4" t="n">
-        <v>-101328000</v>
+        <v>-45443000</v>
       </c>
       <c r="M4" t="n">
-        <v>133963000</v>
+        <v>130342000</v>
       </c>
       <c r="N4" t="n">
-        <v>32635000</v>
+        <v>84899000</v>
       </c>
       <c r="O4" t="n">
-        <v>423170000</v>
+        <v>268846000</v>
       </c>
       <c r="P4" t="n">
-        <v>423170000</v>
+        <v>268846000</v>
       </c>
       <c r="Q4" t="n">
-        <v>6245165000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>6262510000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>28748000</v>
+      </c>
       <c r="S4" t="n">
-        <v>743622000</v>
+        <v>702434000</v>
       </c>
       <c r="T4" t="n">
-        <v>1108937476</v>
+        <v>1105922541</v>
       </c>
       <c r="U4" t="n">
-        <v>1108810921</v>
+        <v>1105815931</v>
       </c>
       <c r="V4" t="n">
-        <v>0.382</v>
+        <v>0.243</v>
       </c>
       <c r="W4" t="n">
-        <v>0.382</v>
+        <v>0.243</v>
       </c>
       <c r="X4" t="n">
-        <v>423170000</v>
+        <v>268846000</v>
       </c>
       <c r="Y4" t="n">
-        <v>423170000</v>
+        <v>268846000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>423170000</v>
+        <v>268846000</v>
       </c>
       <c r="AB4" t="n">
-        <v>244000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>422926000</v>
+        <v>268846000</v>
       </c>
       <c r="AD4" t="n">
-        <v>422926000</v>
+        <v>268846000</v>
       </c>
       <c r="AE4" t="n">
-        <v>176891000</v>
+        <v>184537000</v>
       </c>
       <c r="AF4" t="n">
-        <v>599817000</v>
+        <v>453383000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-101328000</v>
+        <v>-45443000</v>
       </c>
       <c r="AH4" t="n">
-        <v>133963000</v>
+        <v>130342000</v>
       </c>
       <c r="AI4" t="n">
-        <v>32635000</v>
+        <v>84899000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>712120000</v>
+        <v>500374000</v>
       </c>
       <c r="AK4" t="n">
-        <v>3472688000</v>
+        <v>3670856000</v>
       </c>
       <c r="AL4" t="n">
-        <v>988964000</v>
+        <v>1180289000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1831707000</v>
+        <v>1759682000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1831707000</v>
+        <v>1759682000</v>
       </c>
       <c r="AO4" t="n">
-        <v>4184808000</v>
+        <v>4171230000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2772477000</v>
+        <v>2591654000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6957285000</v>
+        <v>6762884000</v>
       </c>
       <c r="AR4" t="n">
-        <v>6957285000</v>
+        <v>6762884000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-11822</v>
+        <v>-1556268</v>
       </c>
       <c r="C5" t="n">
-        <v>0.257</v>
+        <v>0.291</v>
       </c>
       <c r="D5" t="n">
-        <v>2493242000</v>
+        <v>2511557000</v>
       </c>
       <c r="E5" t="n">
-        <v>-46000</v>
+        <v>-5348000</v>
       </c>
       <c r="F5" t="n">
-        <v>-46000</v>
+        <v>-5348000</v>
       </c>
       <c r="G5" t="n">
-        <v>444621000</v>
+        <v>470126000</v>
       </c>
       <c r="H5" t="n">
-        <v>1696036000</v>
+        <v>1643996000</v>
       </c>
       <c r="I5" t="n">
-        <v>2687832000</v>
+        <v>2102263000</v>
       </c>
       <c r="J5" t="n">
-        <v>2493196000</v>
+        <v>2506209000</v>
       </c>
       <c r="K5" t="n">
-        <v>707820000</v>
+        <v>765224000</v>
       </c>
       <c r="L5" t="n">
-        <v>-75934000</v>
+        <v>-34194000</v>
       </c>
       <c r="M5" t="n">
-        <v>111787000</v>
+        <v>102048000</v>
       </c>
       <c r="N5" t="n">
-        <v>35853000</v>
+        <v>67854000</v>
       </c>
       <c r="O5" t="n">
-        <v>444655178</v>
+        <v>473917732</v>
       </c>
       <c r="P5" t="n">
-        <v>444621000</v>
+        <v>470126000</v>
       </c>
       <c r="Q5" t="n">
-        <v>6046638000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>5519595000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>30979000</v>
+      </c>
       <c r="S5" t="n">
-        <v>674215000</v>
+        <v>700602000</v>
       </c>
       <c r="T5" t="n">
-        <v>1114834038</v>
+        <v>1103919740</v>
       </c>
       <c r="U5" t="n">
-        <v>1114587861</v>
+        <v>1103917568</v>
       </c>
       <c r="V5" t="n">
-        <v>0.399</v>
+        <v>0.426</v>
       </c>
       <c r="W5" t="n">
-        <v>0.399</v>
+        <v>0.426</v>
       </c>
       <c r="X5" t="n">
-        <v>444621000</v>
+        <v>470126000</v>
       </c>
       <c r="Y5" t="n">
-        <v>444621000</v>
+        <v>470126000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>444621000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1983000</v>
-      </c>
+        <v>470126000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>442638000</v>
+        <v>470126000</v>
       </c>
       <c r="AD5" t="n">
-        <v>442638000</v>
+        <v>470126000</v>
       </c>
       <c r="AE5" t="n">
-        <v>153395000</v>
+        <v>193050000</v>
       </c>
       <c r="AF5" t="n">
-        <v>596033000</v>
+        <v>663176000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-75934000</v>
+        <v>-34194000</v>
       </c>
       <c r="AH5" t="n">
-        <v>111787000</v>
+        <v>102048000</v>
       </c>
       <c r="AI5" t="n">
-        <v>35853000</v>
+        <v>67854000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>673670000</v>
+        <v>701656000</v>
       </c>
       <c r="AK5" t="n">
-        <v>3358806000</v>
+        <v>3417332000</v>
       </c>
       <c r="AL5" t="n">
-        <v>984748000</v>
+        <v>929145000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1785376000</v>
+        <v>1740985000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1785376000</v>
+        <v>1740985000</v>
       </c>
       <c r="AO5" t="n">
-        <v>4032476000</v>
+        <v>4118988000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2687832000</v>
+        <v>2102263000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6720308000</v>
+        <v>6221251000</v>
       </c>
       <c r="AR5" t="n">
-        <v>6720308000</v>
+        <v>6221251000</v>
       </c>
     </row>
   </sheetData>
@@ -1568,143 +1568,145 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
+        <v>44377</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1102259101</v>
+        <v>1110988601</v>
       </c>
       <c r="D2" t="n">
-        <v>1102259101</v>
+        <v>1110988601</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>963176000</v>
+        <v>2485726000</v>
       </c>
       <c r="G2" t="n">
-        <v>1227573000</v>
+        <v>1999437000</v>
       </c>
       <c r="H2" t="n">
-        <v>5249449000</v>
+        <v>6706933000</v>
       </c>
       <c r="I2" t="n">
-        <v>81401000</v>
+        <v>527990000</v>
       </c>
       <c r="J2" t="n">
-        <v>1227573000</v>
+        <v>1999437000</v>
       </c>
       <c r="K2" t="n">
-        <v>899376000</v>
+        <v>897766000</v>
       </c>
       <c r="L2" t="n">
-        <v>5185649000</v>
+        <v>5118973000</v>
       </c>
       <c r="M2" t="n">
-        <v>5247249000</v>
+        <v>6629744000</v>
       </c>
       <c r="N2" t="n">
-        <v>5185649000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>5097108000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-21865000</v>
+      </c>
       <c r="P2" t="n">
-        <v>5185649000</v>
+        <v>5118973000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1609000</v>
+        <v>6043000</v>
       </c>
       <c r="R2" t="n">
-        <v>4753000</v>
+        <v>14857000</v>
       </c>
       <c r="S2" t="n">
-        <v>3405492000</v>
+        <v>3329063000</v>
       </c>
       <c r="T2" t="n">
-        <v>1666070000</v>
+        <v>1658986000</v>
       </c>
       <c r="U2" t="n">
-        <v>110226000</v>
+        <v>111099000</v>
       </c>
       <c r="V2" t="n">
-        <v>110226000</v>
+        <v>111099000</v>
       </c>
       <c r="W2" t="n">
-        <v>5992626000</v>
+        <v>5552951000</v>
       </c>
       <c r="X2" t="n">
-        <v>3048721000</v>
+        <v>2893005000</v>
       </c>
       <c r="Y2" t="n">
-        <v>2412756000</v>
+        <v>826962000</v>
       </c>
       <c r="Z2" t="n">
-        <v>8496000</v>
+        <v>24640000</v>
       </c>
       <c r="AA2" t="n">
-        <v>158315000</v>
+        <v>111793000</v>
       </c>
       <c r="AB2" t="n">
-        <v>417343000</v>
+        <v>1862236000</v>
       </c>
       <c r="AC2" t="n">
-        <v>355743000</v>
+        <v>351465000</v>
       </c>
       <c r="AD2" t="n">
-        <v>61600000</v>
+        <v>1510771000</v>
       </c>
       <c r="AE2" t="n">
-        <v>51811000</v>
+        <v>67374000</v>
       </c>
       <c r="AF2" t="n">
-        <v>2943905000</v>
+        <v>2659946000</v>
       </c>
       <c r="AG2" t="n">
-        <v>228366000</v>
+        <v>102912000</v>
       </c>
       <c r="AH2" t="n">
-        <v>545833000</v>
+        <v>623490000</v>
       </c>
       <c r="AI2" t="n">
-        <v>543633000</v>
+        <v>546301000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2200000</v>
+        <v>77189000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1269713000</v>
+        <v>1079126000</v>
       </c>
       <c r="AL2" t="n">
-        <v>245699000</v>
+        <v>172060000</v>
       </c>
       <c r="AM2" t="n">
-        <v>657806000</v>
+        <v>492981000</v>
       </c>
       <c r="AN2" t="n">
-        <v>366208000</v>
+        <v>414085000</v>
       </c>
       <c r="AO2" t="n">
-        <v>11178275000</v>
+        <v>10650059000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8152969000</v>
+        <v>7462123000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>93304000</v>
+        <v>76874000</v>
       </c>
       <c r="AR2" t="n">
-        <v>151420000</v>
+        <v>167485000</v>
       </c>
       <c r="AS2" t="n">
-        <v>3128000</v>
+        <v>5585000</v>
       </c>
       <c r="AT2" t="n">
-        <v>34956000</v>
+        <v>439580000</v>
       </c>
       <c r="AU2" t="n">
-        <v>34956000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>16755000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>422825000</v>
+      </c>
       <c r="AW2" t="n">
         <v>3000</v>
       </c>
@@ -1712,222 +1714,230 @@
         <v>3000</v>
       </c>
       <c r="AY2" t="n">
-        <v>3958076000</v>
+        <v>3119536000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3958076000</v>
+        <v>3119536000</v>
       </c>
       <c r="BA2" t="n">
-        <v>3884435000</v>
+        <v>3584489000</v>
       </c>
       <c r="BB2" t="n">
-        <v>-8145055000</v>
+        <v>-7676293000</v>
       </c>
       <c r="BC2" t="n">
-        <v>12029490000</v>
+        <v>11260782000</v>
       </c>
       <c r="BD2" t="n">
-        <v>234478000</v>
+        <v>171325000</v>
       </c>
       <c r="BE2" t="n">
-        <v>9202810000</v>
+        <v>8631659000</v>
       </c>
       <c r="BF2" t="n">
-        <v>2027955000</v>
+        <v>1864765000</v>
       </c>
       <c r="BG2" t="n">
-        <v>557626000</v>
+        <v>583751000</v>
       </c>
       <c r="BH2" t="n">
-        <v>6621000</v>
+        <v>9282000</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3025306000</v>
+        <v>3187936000</v>
       </c>
       <c r="BK2" t="n">
-        <v>259858000</v>
+        <v>211331000</v>
       </c>
       <c r="BL2" t="n">
-        <v>107069000</v>
+        <v>57423000</v>
       </c>
       <c r="BM2" t="n">
-        <v>-2535000</v>
+        <v>-13115000</v>
       </c>
       <c r="BN2" t="n">
-        <v>17949000</v>
+        <v>18945000</v>
       </c>
       <c r="BO2" t="n">
-        <v>91655000</v>
+        <v>51593000</v>
       </c>
       <c r="BP2" t="n">
-        <v>185623000</v>
+        <v>173996000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>384709000</v>
+        <v>253484000</v>
       </c>
       <c r="BR2" t="n">
-        <v>410315000</v>
+        <v>332177000</v>
       </c>
       <c r="BS2" t="n">
-        <v>-5137000</v>
+        <v>-8459000</v>
       </c>
       <c r="BT2" t="n">
-        <v>415452000</v>
+        <v>340636000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1677732000</v>
+        <v>2159525000</v>
       </c>
       <c r="BV2" t="n">
-        <v>100817000</v>
+        <v>64641000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1576915000</v>
-      </c>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
+        <v>2094884000</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1192583000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>902301000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
-      </c>
-      <c r="B3" t="n">
-        <v>4760</v>
-      </c>
+        <v>44742</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1106459841</v>
+        <v>1105792101</v>
       </c>
       <c r="D3" t="n">
-        <v>1106464601</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>1105792101</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1125345000</v>
+      </c>
       <c r="F3" t="n">
-        <v>852994000</v>
+        <v>2415633000</v>
       </c>
       <c r="G3" t="n">
-        <v>653078000</v>
+        <v>249042000</v>
       </c>
       <c r="H3" t="n">
-        <v>5150487000</v>
+        <v>6664596000</v>
       </c>
       <c r="I3" t="n">
-        <v>-301682000</v>
+        <v>-690023000</v>
       </c>
       <c r="J3" t="n">
-        <v>653078000</v>
+        <v>249042000</v>
       </c>
       <c r="K3" t="n">
-        <v>786994000</v>
+        <v>904821000</v>
       </c>
       <c r="L3" t="n">
-        <v>5084487000</v>
+        <v>5153784000</v>
       </c>
       <c r="M3" t="n">
-        <v>5148287000</v>
+        <v>5219784000</v>
       </c>
       <c r="N3" t="n">
-        <v>5084487000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>5153784000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="n">
-        <v>5084487000</v>
+        <v>5153784000</v>
       </c>
       <c r="Q3" t="n">
-        <v>248000</v>
+        <v>1705000</v>
       </c>
       <c r="R3" t="n">
-        <v>5393000</v>
+        <v>14296000</v>
       </c>
       <c r="S3" t="n">
-        <v>3305163000</v>
+        <v>3369301000</v>
       </c>
       <c r="T3" t="n">
-        <v>1665650000</v>
+        <v>1659378000</v>
       </c>
       <c r="U3" t="n">
-        <v>110646000</v>
+        <v>110579000</v>
       </c>
       <c r="V3" t="n">
-        <v>110646000</v>
+        <v>110579000</v>
       </c>
       <c r="W3" t="n">
-        <v>5814456000</v>
+        <v>7427348000</v>
       </c>
       <c r="X3" t="n">
-        <v>3110252000</v>
+        <v>3335920000</v>
       </c>
       <c r="Y3" t="n">
-        <v>2578218000</v>
+        <v>2734426000</v>
       </c>
       <c r="Z3" t="n">
-        <v>6940000</v>
+        <v>14455000</v>
       </c>
       <c r="AA3" t="n">
-        <v>143079000</v>
+        <v>116807000</v>
       </c>
       <c r="AB3" t="n">
-        <v>318706000</v>
+        <v>394522000</v>
       </c>
       <c r="AC3" t="n">
-        <v>254906000</v>
+        <v>328522000</v>
       </c>
       <c r="AD3" t="n">
-        <v>63800000</v>
+        <v>66000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>63309000</v>
+        <v>75710000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2704204000</v>
+        <v>4091428000</v>
       </c>
       <c r="AG3" t="n">
-        <v>222922000</v>
+        <v>217609000</v>
       </c>
       <c r="AH3" t="n">
-        <v>534288000</v>
+        <v>2021111000</v>
       </c>
       <c r="AI3" t="n">
-        <v>532088000</v>
+        <v>576299000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2200000</v>
+        <v>1444812000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1107548000</v>
+        <v>986252000</v>
       </c>
       <c r="AL3" t="n">
-        <v>179048000</v>
+        <v>189481000</v>
       </c>
       <c r="AM3" t="n">
-        <v>611198000</v>
+        <v>557318000</v>
       </c>
       <c r="AN3" t="n">
-        <v>317302000</v>
+        <v>239453000</v>
       </c>
       <c r="AO3" t="n">
-        <v>10898943000</v>
+        <v>12581132000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8496421000</v>
+        <v>9179727000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>101702000</v>
+        <v>87608000</v>
       </c>
       <c r="AR3" t="n">
-        <v>79326000</v>
+        <v>130145000</v>
       </c>
       <c r="AS3" t="n">
-        <v>6447000</v>
+        <v>7468000</v>
       </c>
       <c r="AT3" t="n">
-        <v>155123000</v>
+        <v>353167000</v>
       </c>
       <c r="AU3" t="n">
-        <v>155123000</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
+        <v>353167000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>336973000</v>
+      </c>
       <c r="AW3" t="n">
         <v>3000</v>
       </c>
@@ -1935,230 +1945,226 @@
         <v>3000</v>
       </c>
       <c r="AY3" t="n">
-        <v>4431409000</v>
+        <v>4904742000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4431409000</v>
+        <v>4904742000</v>
       </c>
       <c r="BA3" t="n">
-        <v>3690170000</v>
+        <v>3653847000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-8415204000</v>
+        <v>-8139371000</v>
       </c>
       <c r="BC3" t="n">
-        <v>12105374000</v>
+        <v>11793218000</v>
       </c>
       <c r="BD3" t="n">
-        <v>154075000</v>
+        <v>189133000</v>
       </c>
       <c r="BE3" t="n">
-        <v>9518754000</v>
+        <v>9118833000</v>
       </c>
       <c r="BF3" t="n">
-        <v>1883645000</v>
+        <v>1923959000</v>
       </c>
       <c r="BG3" t="n">
-        <v>541723000</v>
+        <v>552880000</v>
       </c>
       <c r="BH3" t="n">
-        <v>7177000</v>
+        <v>8413000</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2402522000</v>
+        <v>3401405000</v>
       </c>
       <c r="BK3" t="n">
-        <v>252548000</v>
+        <v>243751000</v>
       </c>
       <c r="BL3" t="n">
-        <v>106333000</v>
+        <v>100036000</v>
       </c>
       <c r="BM3" t="n">
-        <v>-4523000</v>
+        <v>-4648000</v>
       </c>
       <c r="BN3" t="n">
-        <v>23701000</v>
+        <v>22036000</v>
       </c>
       <c r="BO3" t="n">
-        <v>87155000</v>
+        <v>82648000</v>
       </c>
       <c r="BP3" t="n">
-        <v>155852000</v>
+        <v>170714000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>359549000</v>
+        <v>347796000</v>
       </c>
       <c r="BR3" t="n">
-        <v>351339000</v>
+        <v>343809000</v>
       </c>
       <c r="BS3" t="n">
-        <v>-6290000</v>
+        <v>-6818000</v>
       </c>
       <c r="BT3" t="n">
-        <v>357629000</v>
+        <v>350627000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1176901000</v>
+        <v>2195299000</v>
       </c>
       <c r="BV3" t="n">
-        <v>21749000</v>
+        <v>1809832000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1155152000</v>
+        <v>385467000</v>
       </c>
       <c r="BX3" t="n">
-        <v>1104319000</v>
+        <v>341443000</v>
       </c>
       <c r="BY3" t="n">
-        <v>50833000</v>
+        <v>44024000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45107</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4760</v>
+      </c>
       <c r="C4" t="n">
-        <v>1105792101</v>
+        <v>1106459841</v>
       </c>
       <c r="D4" t="n">
-        <v>1105792101</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1125345000</v>
-      </c>
+        <v>1106464601</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>2415633000</v>
+        <v>852994000</v>
       </c>
       <c r="G4" t="n">
-        <v>249042000</v>
+        <v>653078000</v>
       </c>
       <c r="H4" t="n">
-        <v>6664596000</v>
+        <v>5150487000</v>
       </c>
       <c r="I4" t="n">
-        <v>-690023000</v>
+        <v>-301682000</v>
       </c>
       <c r="J4" t="n">
-        <v>249042000</v>
+        <v>653078000</v>
       </c>
       <c r="K4" t="n">
-        <v>904821000</v>
+        <v>786994000</v>
       </c>
       <c r="L4" t="n">
-        <v>5153784000</v>
+        <v>5084487000</v>
       </c>
       <c r="M4" t="n">
-        <v>5219784000</v>
+        <v>5148287000</v>
       </c>
       <c r="N4" t="n">
-        <v>5153784000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
+        <v>5084487000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>5153784000</v>
+        <v>5084487000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1705000</v>
+        <v>248000</v>
       </c>
       <c r="R4" t="n">
-        <v>14296000</v>
+        <v>5393000</v>
       </c>
       <c r="S4" t="n">
-        <v>3369301000</v>
+        <v>3305163000</v>
       </c>
       <c r="T4" t="n">
-        <v>1659378000</v>
+        <v>1665650000</v>
       </c>
       <c r="U4" t="n">
-        <v>110579000</v>
+        <v>110646000</v>
       </c>
       <c r="V4" t="n">
-        <v>110579000</v>
+        <v>110646000</v>
       </c>
       <c r="W4" t="n">
-        <v>7427348000</v>
+        <v>5814456000</v>
       </c>
       <c r="X4" t="n">
-        <v>3335920000</v>
+        <v>3110252000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2734426000</v>
+        <v>2578218000</v>
       </c>
       <c r="Z4" t="n">
-        <v>14455000</v>
+        <v>6940000</v>
       </c>
       <c r="AA4" t="n">
-        <v>116807000</v>
+        <v>143079000</v>
       </c>
       <c r="AB4" t="n">
-        <v>394522000</v>
+        <v>318706000</v>
       </c>
       <c r="AC4" t="n">
-        <v>328522000</v>
+        <v>254906000</v>
       </c>
       <c r="AD4" t="n">
-        <v>66000000</v>
+        <v>63800000</v>
       </c>
       <c r="AE4" t="n">
-        <v>75710000</v>
+        <v>63309000</v>
       </c>
       <c r="AF4" t="n">
-        <v>4091428000</v>
+        <v>2704204000</v>
       </c>
       <c r="AG4" t="n">
-        <v>217609000</v>
+        <v>222922000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2021111000</v>
+        <v>534288000</v>
       </c>
       <c r="AI4" t="n">
-        <v>576299000</v>
+        <v>532088000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1444812000</v>
+        <v>2200000</v>
       </c>
       <c r="AK4" t="n">
-        <v>986252000</v>
+        <v>1107548000</v>
       </c>
       <c r="AL4" t="n">
-        <v>189481000</v>
+        <v>179048000</v>
       </c>
       <c r="AM4" t="n">
-        <v>557318000</v>
+        <v>611198000</v>
       </c>
       <c r="AN4" t="n">
-        <v>239453000</v>
+        <v>317302000</v>
       </c>
       <c r="AO4" t="n">
-        <v>12581132000</v>
+        <v>10898943000</v>
       </c>
       <c r="AP4" t="n">
-        <v>9179727000</v>
+        <v>8496421000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>87608000</v>
+        <v>101702000</v>
       </c>
       <c r="AR4" t="n">
-        <v>130145000</v>
+        <v>79326000</v>
       </c>
       <c r="AS4" t="n">
-        <v>7468000</v>
+        <v>6447000</v>
       </c>
       <c r="AT4" t="n">
-        <v>353167000</v>
+        <v>155123000</v>
       </c>
       <c r="AU4" t="n">
-        <v>353167000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>336973000</v>
-      </c>
+        <v>155123000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
         <v>3000</v>
       </c>
@@ -2166,228 +2172,226 @@
         <v>3000</v>
       </c>
       <c r="AY4" t="n">
-        <v>4904742000</v>
+        <v>4431409000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4904742000</v>
+        <v>4431409000</v>
       </c>
       <c r="BA4" t="n">
-        <v>3653847000</v>
+        <v>3690170000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-8139371000</v>
+        <v>-8415204000</v>
       </c>
       <c r="BC4" t="n">
-        <v>11793218000</v>
+        <v>12105374000</v>
       </c>
       <c r="BD4" t="n">
-        <v>189133000</v>
+        <v>154075000</v>
       </c>
       <c r="BE4" t="n">
-        <v>9118833000</v>
+        <v>9518754000</v>
       </c>
       <c r="BF4" t="n">
-        <v>1923959000</v>
+        <v>1883645000</v>
       </c>
       <c r="BG4" t="n">
-        <v>552880000</v>
+        <v>541723000</v>
       </c>
       <c r="BH4" t="n">
-        <v>8413000</v>
+        <v>7177000</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3401405000</v>
+        <v>2402522000</v>
       </c>
       <c r="BK4" t="n">
-        <v>243751000</v>
+        <v>252548000</v>
       </c>
       <c r="BL4" t="n">
-        <v>100036000</v>
+        <v>106333000</v>
       </c>
       <c r="BM4" t="n">
-        <v>-4648000</v>
+        <v>-4523000</v>
       </c>
       <c r="BN4" t="n">
-        <v>22036000</v>
+        <v>23701000</v>
       </c>
       <c r="BO4" t="n">
-        <v>82648000</v>
+        <v>87155000</v>
       </c>
       <c r="BP4" t="n">
-        <v>170714000</v>
+        <v>155852000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>347796000</v>
+        <v>359549000</v>
       </c>
       <c r="BR4" t="n">
-        <v>343809000</v>
+        <v>351339000</v>
       </c>
       <c r="BS4" t="n">
-        <v>-6818000</v>
+        <v>-6290000</v>
       </c>
       <c r="BT4" t="n">
-        <v>350627000</v>
+        <v>357629000</v>
       </c>
       <c r="BU4" t="n">
-        <v>2195299000</v>
+        <v>1176901000</v>
       </c>
       <c r="BV4" t="n">
-        <v>1809832000</v>
+        <v>21749000</v>
       </c>
       <c r="BW4" t="n">
-        <v>385467000</v>
+        <v>1155152000</v>
       </c>
       <c r="BX4" t="n">
-        <v>341443000</v>
+        <v>1104319000</v>
       </c>
       <c r="BY4" t="n">
-        <v>44024000</v>
+        <v>50833000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45473</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="n">
-        <v>1110988601</v>
+        <v>1102259101</v>
       </c>
       <c r="D5" t="n">
-        <v>1110988601</v>
+        <v>1102259101</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2485726000</v>
+        <v>963176000</v>
       </c>
       <c r="G5" t="n">
-        <v>1999437000</v>
+        <v>1227573000</v>
       </c>
       <c r="H5" t="n">
-        <v>6706933000</v>
+        <v>5249449000</v>
       </c>
       <c r="I5" t="n">
-        <v>527990000</v>
+        <v>81401000</v>
       </c>
       <c r="J5" t="n">
-        <v>1999437000</v>
+        <v>1227573000</v>
       </c>
       <c r="K5" t="n">
-        <v>897766000</v>
+        <v>899376000</v>
       </c>
       <c r="L5" t="n">
-        <v>5118973000</v>
+        <v>5185649000</v>
       </c>
       <c r="M5" t="n">
-        <v>6629744000</v>
+        <v>5247249000</v>
       </c>
       <c r="N5" t="n">
-        <v>5097108000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-21865000</v>
-      </c>
+        <v>5185649000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>5118973000</v>
+        <v>5185649000</v>
       </c>
       <c r="Q5" t="n">
-        <v>6043000</v>
+        <v>1609000</v>
       </c>
       <c r="R5" t="n">
-        <v>14857000</v>
+        <v>4753000</v>
       </c>
       <c r="S5" t="n">
-        <v>3329063000</v>
+        <v>3405492000</v>
       </c>
       <c r="T5" t="n">
-        <v>1658986000</v>
+        <v>1666070000</v>
       </c>
       <c r="U5" t="n">
-        <v>111099000</v>
+        <v>110226000</v>
       </c>
       <c r="V5" t="n">
-        <v>111099000</v>
+        <v>110226000</v>
       </c>
       <c r="W5" t="n">
-        <v>5552951000</v>
+        <v>5992626000</v>
       </c>
       <c r="X5" t="n">
-        <v>2893005000</v>
+        <v>3048721000</v>
       </c>
       <c r="Y5" t="n">
-        <v>826962000</v>
+        <v>2412756000</v>
       </c>
       <c r="Z5" t="n">
-        <v>24640000</v>
+        <v>8496000</v>
       </c>
       <c r="AA5" t="n">
-        <v>111793000</v>
+        <v>158315000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1862236000</v>
+        <v>417343000</v>
       </c>
       <c r="AC5" t="n">
-        <v>351465000</v>
+        <v>355743000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1510771000</v>
+        <v>61600000</v>
       </c>
       <c r="AE5" t="n">
-        <v>67374000</v>
+        <v>51811000</v>
       </c>
       <c r="AF5" t="n">
-        <v>2659946000</v>
+        <v>2943905000</v>
       </c>
       <c r="AG5" t="n">
-        <v>102912000</v>
+        <v>228366000</v>
       </c>
       <c r="AH5" t="n">
-        <v>623490000</v>
+        <v>545833000</v>
       </c>
       <c r="AI5" t="n">
-        <v>546301000</v>
+        <v>543633000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>77189000</v>
+        <v>2200000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1079126000</v>
+        <v>1269713000</v>
       </c>
       <c r="AL5" t="n">
-        <v>172060000</v>
+        <v>245699000</v>
       </c>
       <c r="AM5" t="n">
-        <v>492981000</v>
+        <v>657806000</v>
       </c>
       <c r="AN5" t="n">
-        <v>414085000</v>
+        <v>366208000</v>
       </c>
       <c r="AO5" t="n">
-        <v>10650059000</v>
+        <v>11178275000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7462123000</v>
+        <v>8152969000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>76874000</v>
+        <v>93304000</v>
       </c>
       <c r="AR5" t="n">
-        <v>167485000</v>
+        <v>151420000</v>
       </c>
       <c r="AS5" t="n">
-        <v>5585000</v>
+        <v>3128000</v>
       </c>
       <c r="AT5" t="n">
-        <v>439580000</v>
+        <v>34956000</v>
       </c>
       <c r="AU5" t="n">
-        <v>16755000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>422825000</v>
-      </c>
+        <v>34956000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
         <v>3000</v>
       </c>
@@ -2395,86 +2399,82 @@
         <v>3000</v>
       </c>
       <c r="AY5" t="n">
-        <v>3119536000</v>
+        <v>3958076000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3119536000</v>
+        <v>3958076000</v>
       </c>
       <c r="BA5" t="n">
-        <v>3584489000</v>
+        <v>3884435000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-7676293000</v>
+        <v>-8145055000</v>
       </c>
       <c r="BC5" t="n">
-        <v>11260782000</v>
+        <v>12029490000</v>
       </c>
       <c r="BD5" t="n">
-        <v>171325000</v>
+        <v>234478000</v>
       </c>
       <c r="BE5" t="n">
-        <v>8631659000</v>
+        <v>9202810000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1864765000</v>
+        <v>2027955000</v>
       </c>
       <c r="BG5" t="n">
-        <v>583751000</v>
+        <v>557626000</v>
       </c>
       <c r="BH5" t="n">
-        <v>9282000</v>
+        <v>6621000</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>3187936000</v>
+        <v>3025306000</v>
       </c>
       <c r="BK5" t="n">
-        <v>211331000</v>
+        <v>259858000</v>
       </c>
       <c r="BL5" t="n">
-        <v>57423000</v>
+        <v>107069000</v>
       </c>
       <c r="BM5" t="n">
-        <v>-13115000</v>
+        <v>-2535000</v>
       </c>
       <c r="BN5" t="n">
-        <v>18945000</v>
+        <v>17949000</v>
       </c>
       <c r="BO5" t="n">
-        <v>51593000</v>
+        <v>91655000</v>
       </c>
       <c r="BP5" t="n">
-        <v>173996000</v>
+        <v>185623000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>253484000</v>
+        <v>384709000</v>
       </c>
       <c r="BR5" t="n">
-        <v>332177000</v>
+        <v>410315000</v>
       </c>
       <c r="BS5" t="n">
-        <v>-8459000</v>
+        <v>-5137000</v>
       </c>
       <c r="BT5" t="n">
-        <v>340636000</v>
+        <v>415452000</v>
       </c>
       <c r="BU5" t="n">
-        <v>2159525000</v>
+        <v>1677732000</v>
       </c>
       <c r="BV5" t="n">
-        <v>64641000</v>
+        <v>100817000</v>
       </c>
       <c r="BW5" t="n">
-        <v>2094884000</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1192583000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>902301000</v>
-      </c>
+        <v>1576915000</v>
+      </c>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2739,586 +2739,586 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>1335197000</v>
+        <v>1450069000</v>
       </c>
       <c r="C2" t="n">
-        <v>-16676000</v>
+        <v>-47328000</v>
       </c>
       <c r="D2" t="n">
-        <v>-2200000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>-222783000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-6785000</v>
       </c>
       <c r="G2" t="n">
-        <v>-826544000</v>
+        <v>-970362000</v>
       </c>
       <c r="H2" t="n">
-        <v>1576915000</v>
+        <v>2094884000</v>
       </c>
       <c r="I2" t="n">
-        <v>1155152000</v>
+        <v>2127409000</v>
       </c>
       <c r="J2" t="n">
-        <v>-4000</v>
+        <v>781000</v>
       </c>
       <c r="K2" t="n">
-        <v>421767000</v>
+        <v>-33306000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1018064000</v>
+        <v>-1317784000</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-353121000</v>
+        <v>-328405000</v>
       </c>
       <c r="O2" t="n">
-        <v>-353121000</v>
+        <v>-328405000</v>
       </c>
       <c r="P2" t="n">
-        <v>-16676000</v>
+        <v>-54113000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-16676000</v>
+        <v>-47328000</v>
       </c>
       <c r="R2" t="n">
+        <v>-6785000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-222783000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-222783000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-222783000</v>
+      </c>
+      <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="n">
-        <v>-2200000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-2200000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-2200000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>-721910000</v>
+        <v>-1135953000</v>
       </c>
       <c r="X2" t="n">
-        <v>-224999000</v>
+        <v>-119855000</v>
       </c>
       <c r="Y2" t="n">
-        <v>66461000</v>
+        <v>38235000</v>
       </c>
       <c r="Z2" t="n">
-        <v>36835000</v>
+        <v>-204170000</v>
       </c>
       <c r="AA2" t="n">
-        <v>36835000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>302423000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-506593000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>-224999000</v>
+        <v>-119855000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-224999000</v>
+        <v>-119855000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-600207000</v>
+        <v>-850163000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1338000</v>
+        <v>344000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-601545000</v>
+        <v>-850507000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2161741000</v>
+        <v>2420431000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-127892000</v>
+        <v>-129851000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-37105000</v>
+        <v>-85698000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-91051000</v>
+        <v>169050000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-79166000</v>
+        <v>-71289000</v>
       </c>
       <c r="AM2" t="n">
-        <v>110103000</v>
+        <v>85088000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-736000</v>
+        <v>2222000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-121252000</v>
+        <v>153029000</v>
       </c>
       <c r="AP2" t="n">
-        <v>122251000</v>
+        <v>148600000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1361000</v>
+        <v>8461000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1643996000</v>
+        <v>1696036000</v>
       </c>
       <c r="AS2" t="n">
-        <v>473333000</v>
+        <v>325552000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1170663000</v>
+        <v>1370484000</v>
       </c>
       <c r="AU2" t="n">
-        <v>2378000</v>
+        <v>46000</v>
       </c>
       <c r="AV2" t="n">
-        <v>361000</v>
+        <v>1657000</v>
       </c>
       <c r="AW2" t="n">
-        <v>9425000</v>
+        <v>17219000</v>
       </c>
       <c r="AX2" t="n">
-        <v>663176000</v>
+        <v>596033000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>1325952000</v>
+        <v>1071798000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1463000</v>
+        <v>-22360000</v>
       </c>
       <c r="D3" t="n">
-        <v>-1446439000</v>
+        <v>-96425000</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>3029000</v>
+        <v>-3563000</v>
       </c>
       <c r="G3" t="n">
-        <v>-928410000</v>
+        <v>-964358000</v>
       </c>
       <c r="H3" t="n">
-        <v>1155152000</v>
+        <v>385467000</v>
       </c>
       <c r="I3" t="n">
-        <v>385467000</v>
+        <v>2094884000</v>
       </c>
       <c r="J3" t="n">
-        <v>-181000</v>
+        <v>75000</v>
       </c>
       <c r="K3" t="n">
-        <v>769866000</v>
+        <v>-1709492000</v>
       </c>
       <c r="L3" t="n">
-        <v>-2415480000</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>-1124010000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-8797000</v>
+      </c>
       <c r="N3" t="n">
-        <v>-331762000</v>
+        <v>-332853000</v>
       </c>
       <c r="O3" t="n">
-        <v>-331762000</v>
+        <v>-332853000</v>
       </c>
       <c r="P3" t="n">
-        <v>1566000</v>
+        <v>-25923000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1463000</v>
+        <v>-22360000</v>
       </c>
       <c r="R3" t="n">
-        <v>3029000</v>
+        <v>-3563000</v>
       </c>
       <c r="S3" t="n">
-        <v>-1446439000</v>
+        <v>-96425000</v>
       </c>
       <c r="T3" t="n">
-        <v>-1446439000</v>
+        <v>-96425000</v>
       </c>
       <c r="U3" t="n">
-        <v>-1446439000</v>
+        <v>-96425000</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>930984000</v>
+        <v>-2621638000</v>
       </c>
       <c r="X3" t="n">
-        <v>-219636000</v>
+        <v>-252682000</v>
       </c>
       <c r="Y3" t="n">
-        <v>80760000</v>
+        <v>35568000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1778062000</v>
+        <v>-1692921000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1778062000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+        <v>62128000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1755049000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-252682000</v>
+      </c>
       <c r="AD3" t="n">
-        <v>-219636000</v>
+        <v>-252682000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-708202000</v>
+        <v>-711603000</v>
       </c>
       <c r="AF3" t="n">
-        <v>572000</v>
+        <v>73000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-708774000</v>
+        <v>-711676000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2254362000</v>
+        <v>2036156000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-103354000</v>
+        <v>-109416000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-73377000</v>
+        <v>-73022000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-21364000</v>
+        <v>-264707000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-101427000</v>
+        <v>-91107000</v>
       </c>
       <c r="AM3" t="n">
-        <v>22694000</v>
+        <v>-152585000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-6297000</v>
+        <v>-42613000</v>
       </c>
       <c r="AO3" t="n">
-        <v>63666000</v>
+        <v>21598000</v>
       </c>
       <c r="AP3" t="n">
-        <v>133579000</v>
+        <v>182203000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2094000</v>
+        <v>2284000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1666056000</v>
+        <v>1740087000</v>
       </c>
       <c r="AS3" t="n">
-        <v>473333000</v>
+        <v>431828000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1192723000</v>
+        <v>1308259000</v>
       </c>
       <c r="AU3" t="n">
-        <v>201257000</v>
+        <v>31000000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1548000</v>
+        <v>10975000</v>
       </c>
       <c r="AW3" t="n">
-        <v>6293000</v>
+        <v>11247000</v>
       </c>
       <c r="AX3" t="n">
-        <v>453383000</v>
+        <v>599817000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>1071798000</v>
+        <v>1325952000</v>
       </c>
       <c r="C4" t="n">
-        <v>-22360000</v>
+        <v>-1463000</v>
       </c>
       <c r="D4" t="n">
-        <v>-96425000</v>
+        <v>-1446439000</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-3563000</v>
+        <v>3029000</v>
       </c>
       <c r="G4" t="n">
-        <v>-964358000</v>
+        <v>-928410000</v>
       </c>
       <c r="H4" t="n">
+        <v>1155152000</v>
+      </c>
+      <c r="I4" t="n">
         <v>385467000</v>
       </c>
-      <c r="I4" t="n">
-        <v>2094884000</v>
-      </c>
       <c r="J4" t="n">
-        <v>75000</v>
+        <v>-181000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1709492000</v>
+        <v>769866000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1124010000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-8797000</v>
-      </c>
+        <v>-2415480000</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>-332853000</v>
+        <v>-331762000</v>
       </c>
       <c r="O4" t="n">
-        <v>-332853000</v>
+        <v>-331762000</v>
       </c>
       <c r="P4" t="n">
-        <v>-25923000</v>
+        <v>1566000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-22360000</v>
+        <v>-1463000</v>
       </c>
       <c r="R4" t="n">
-        <v>-3563000</v>
+        <v>3029000</v>
       </c>
       <c r="S4" t="n">
-        <v>-96425000</v>
+        <v>-1446439000</v>
       </c>
       <c r="T4" t="n">
-        <v>-96425000</v>
+        <v>-1446439000</v>
       </c>
       <c r="U4" t="n">
-        <v>-96425000</v>
+        <v>-1446439000</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-2621638000</v>
+        <v>930984000</v>
       </c>
       <c r="X4" t="n">
-        <v>-252682000</v>
+        <v>-219636000</v>
       </c>
       <c r="Y4" t="n">
-        <v>35568000</v>
+        <v>80760000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1692921000</v>
+        <v>1778062000</v>
       </c>
       <c r="AA4" t="n">
-        <v>62128000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-1755049000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-252682000</v>
-      </c>
+        <v>1778062000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-252682000</v>
+        <v>-219636000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-711603000</v>
+        <v>-708202000</v>
       </c>
       <c r="AF4" t="n">
-        <v>73000</v>
+        <v>572000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-711676000</v>
+        <v>-708774000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2036156000</v>
+        <v>2254362000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-109416000</v>
+        <v>-103354000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-73022000</v>
+        <v>-73377000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-264707000</v>
+        <v>-21364000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-91107000</v>
+        <v>-101427000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-152585000</v>
+        <v>22694000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-42613000</v>
+        <v>-6297000</v>
       </c>
       <c r="AO4" t="n">
-        <v>21598000</v>
+        <v>63666000</v>
       </c>
       <c r="AP4" t="n">
-        <v>182203000</v>
+        <v>133579000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2284000</v>
+        <v>2094000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1740087000</v>
+        <v>1666056000</v>
       </c>
       <c r="AS4" t="n">
-        <v>431828000</v>
+        <v>473333000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1308259000</v>
+        <v>1192723000</v>
       </c>
       <c r="AU4" t="n">
-        <v>31000000</v>
+        <v>201257000</v>
       </c>
       <c r="AV4" t="n">
-        <v>10975000</v>
+        <v>1548000</v>
       </c>
       <c r="AW4" t="n">
-        <v>11247000</v>
+        <v>6293000</v>
       </c>
       <c r="AX4" t="n">
-        <v>599817000</v>
+        <v>453383000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>1450069000</v>
+        <v>1335197000</v>
       </c>
       <c r="C5" t="n">
-        <v>-47328000</v>
+        <v>-16676000</v>
       </c>
       <c r="D5" t="n">
-        <v>-222783000</v>
-      </c>
-      <c r="E5" t="n">
+        <v>-2200000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
-        <v>-6785000</v>
-      </c>
       <c r="G5" t="n">
-        <v>-970362000</v>
+        <v>-826544000</v>
       </c>
       <c r="H5" t="n">
-        <v>2094884000</v>
+        <v>1576915000</v>
       </c>
       <c r="I5" t="n">
-        <v>2127409000</v>
+        <v>1155152000</v>
       </c>
       <c r="J5" t="n">
-        <v>781000</v>
+        <v>-4000</v>
       </c>
       <c r="K5" t="n">
-        <v>-33306000</v>
+        <v>421767000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1317784000</v>
+        <v>-1018064000</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>-328405000</v>
+        <v>-353121000</v>
       </c>
       <c r="O5" t="n">
-        <v>-328405000</v>
+        <v>-353121000</v>
       </c>
       <c r="P5" t="n">
-        <v>-54113000</v>
+        <v>-16676000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-47328000</v>
+        <v>-16676000</v>
       </c>
       <c r="R5" t="n">
-        <v>-6785000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-222783000</v>
+        <v>-2200000</v>
       </c>
       <c r="T5" t="n">
-        <v>-222783000</v>
+        <v>-2200000</v>
       </c>
       <c r="U5" t="n">
-        <v>-222783000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
+        <v>-2200000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>-1135953000</v>
+        <v>-721910000</v>
       </c>
       <c r="X5" t="n">
-        <v>-119855000</v>
+        <v>-224999000</v>
       </c>
       <c r="Y5" t="n">
-        <v>38235000</v>
+        <v>66461000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-204170000</v>
+        <v>36835000</v>
       </c>
       <c r="AA5" t="n">
-        <v>302423000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-506593000</v>
-      </c>
+        <v>36835000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-119855000</v>
+        <v>-224999000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-119855000</v>
+        <v>-224999000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-850163000</v>
+        <v>-600207000</v>
       </c>
       <c r="AF5" t="n">
-        <v>344000</v>
+        <v>1338000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-850507000</v>
+        <v>-601545000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2420431000</v>
+        <v>2161741000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-129851000</v>
+        <v>-127892000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-85698000</v>
+        <v>-37105000</v>
       </c>
       <c r="AK5" t="n">
-        <v>169050000</v>
+        <v>-91051000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-71289000</v>
+        <v>-79166000</v>
       </c>
       <c r="AM5" t="n">
-        <v>85088000</v>
+        <v>110103000</v>
       </c>
       <c r="AN5" t="n">
-        <v>2222000</v>
+        <v>-736000</v>
       </c>
       <c r="AO5" t="n">
-        <v>153029000</v>
+        <v>-121252000</v>
       </c>
       <c r="AP5" t="n">
-        <v>148600000</v>
+        <v>122251000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8461000</v>
+        <v>1361000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1696036000</v>
+        <v>1643996000</v>
       </c>
       <c r="AS5" t="n">
-        <v>325552000</v>
+        <v>473333000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1370484000</v>
+        <v>1170663000</v>
       </c>
       <c r="AU5" t="n">
-        <v>46000</v>
+        <v>2378000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1657000</v>
+        <v>361000</v>
       </c>
       <c r="AW5" t="n">
-        <v>17219000</v>
+        <v>9425000</v>
       </c>
       <c r="AX5" t="n">
-        <v>596033000</v>
+        <v>663176000</v>
       </c>
     </row>
   </sheetData>
@@ -3903,202 +3903,202 @@
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
       <c r="EX1" t="inlineStr">
@@ -4201,34 +4201,34 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>5.01</v>
+        <v>4.71</v>
       </c>
       <c r="V2" t="n">
-        <v>5.04</v>
+        <v>4.7</v>
       </c>
       <c r="W2" t="n">
-        <v>4.98</v>
+        <v>4.63</v>
       </c>
       <c r="X2" t="n">
-        <v>5.09</v>
+        <v>4.72</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.01</v>
+        <v>4.71</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.04</v>
+        <v>4.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.98</v>
+        <v>4.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.09</v>
+        <v>4.72</v>
       </c>
       <c r="AC2" t="n">
         <v>0.29</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.79</v>
+        <v>6.24</v>
       </c>
       <c r="AE2" t="n">
         <v>1772755200</v>
@@ -4240,34 +4240,34 @@
         <v>7.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.216</v>
+        <v>0.21</v>
       </c>
       <c r="AI2" t="n">
-        <v>11.311111</v>
+        <v>10.333334</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11.311111</v>
+        <v>10.333334</v>
       </c>
       <c r="AK2" t="n">
-        <v>1203500</v>
+        <v>764992</v>
       </c>
       <c r="AL2" t="n">
-        <v>1203500</v>
+        <v>764992</v>
       </c>
       <c r="AM2" t="n">
-        <v>980957</v>
+        <v>926655</v>
       </c>
       <c r="AN2" t="n">
-        <v>2779957</v>
+        <v>758025</v>
       </c>
       <c r="AO2" t="n">
-        <v>2779957</v>
+        <v>758025</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.07</v>
+        <v>4.67</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.08</v>
+        <v>4.7</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -4276,10 +4276,10 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>5603843584</v>
+        <v>5119425024</v>
       </c>
       <c r="AU2" t="n">
-        <v>5515767521</v>
+        <v>5185482040</v>
       </c>
       <c r="AV2" t="n">
         <v>4.24</v>
@@ -4294,19 +4294,19 @@
         <v>1.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.8862358299999999</v>
+        <v>0.80962604</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.0202</v>
+        <v>4.9884</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.8751</v>
+        <v>4.8895</v>
       </c>
       <c r="BC2" t="n">
         <v>0.32</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.06387225000000001</v>
+        <v>0.06794055</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>3740365568</v>
+        <v>3255947008</v>
       </c>
       <c r="BH2" t="n">
         <v>0.07915999999999999</v>
@@ -4332,7 +4332,7 @@
         <v>0.73765</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.041589998</v>
+        <v>0.0396</v>
       </c>
       <c r="BM2" t="n">
         <v>1100951601</v>
@@ -4341,7 +4341,7 @@
         <v>4.897</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.0394119</v>
+        <v>0.949561</v>
       </c>
       <c r="BP2" t="n">
         <v>1751241600</v>
@@ -4376,16 +4376,16 @@
         <v>1300838400</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.592</v>
+        <v>0.515</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.192</v>
+        <v>1.908</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.12837839</v>
+        <v>0.100467324</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="CD2" t="n">
         <v>0.145</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="CG2" t="n">
-        <v>5.09</v>
+        <v>4.65</v>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
@@ -4501,149 +4501,149 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>946949400000</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.059999943</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>4.63 - 4.72</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>926655</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.41000032</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.096698195</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>4.24 - 5.3</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.6500001</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.122641526</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>10.046732</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1756724340</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1757332800</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1740578400</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1740578400</v>
+      </c>
+      <c r="DZ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.3383999</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.06783736</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.23950005</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.04898252</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>finmb_112388</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EM2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-1.2738842</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>SMARTONE TELE</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>SmarTone Telecommunications Holdings Limited</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>finmb_112388</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
+      <c r="EV2" t="n">
+        <v>1782115692</v>
+      </c>
+      <c r="EW2" t="b">
         <v>0</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>SmarTone Telecommunications Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1.5968047</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>SMARTONE TELE</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.07999992</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>4.98 - 5.09</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>980957</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.8500004</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.2004718</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>4.24 - 5.3</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.21000004</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.039622646</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>12.837839</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1756724340</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1757332800</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1740578400</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>1740578400</v>
-      </c>
-      <c r="EM2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0.06980038</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>0.013903904</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>0.21490002</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>0.044081148</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>946949400000</v>
       </c>
       <c r="EX2" t="inlineStr"/>
     </row>
